--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -1,129 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python Automation\egram_bot\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EDCF11-B817-4C76-BCF7-43626E51519D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="eGram Activity Data" sheetId="1" r:id="rId1"/>
+    <sheet name="eGram Activity Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Automation_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>theme</t>
-  </si>
-  <si>
-    <t>activity_name</t>
-  </si>
-  <si>
-    <t>focus_area</t>
-  </si>
-  <si>
-    <t>activity_type</t>
-  </si>
-  <si>
-    <t>activity_description</t>
-  </si>
-  <si>
-    <t>pdi_indicator</t>
-  </si>
-  <si>
-    <t>activity_for</t>
-  </si>
-  <si>
-    <t>targeted_populace</t>
-  </si>
-  <si>
-    <t>activity_nature</t>
-  </si>
-  <si>
-    <t>major_head</t>
-  </si>
-  <si>
-    <t>minor_head</t>
-  </si>
-  <si>
-    <t>is_directly_funded_by_panchayat</t>
-  </si>
-  <si>
-    <t>estimated_completion_year</t>
-  </si>
-  <si>
-    <t>estimated_completion_month</t>
-  </si>
-  <si>
-    <t>estimated_completion_days</t>
-  </si>
-  <si>
-    <t>start_year</t>
-  </si>
-  <si>
-    <t>start_month</t>
-  </si>
-  <si>
-    <t>expected_beneficiary_general</t>
-  </si>
-  <si>
-    <t>expected_beneficiary_sc</t>
-  </si>
-  <si>
-    <t>expected_beneficiary_st</t>
-  </si>
-  <si>
-    <t>estimated_total_cost</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>processed_time</t>
-  </si>
-  <si>
-    <t>error_message</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
       <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED7D31"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,42 +80,124 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -460,104 +485,1910 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
-    <col min="19" max="20" width="9" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="20" customWidth="1"/>
-    <col min="24" max="24" width="60" customWidth="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>activity_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>focus_area</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>activity_type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>activity_description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pdi_indicator</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>activity_for</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>targeted_populace</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>activity_nature</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>is_directly_funded_by_panchayat</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_completion_year</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_completion_month</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_completion_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>start_year</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>start_month</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>expected_beneficiary_general</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>expected_beneficiary_sc</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>expected_beneficiary_st</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_total_cost</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>processed_time</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>error_message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:37:26</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:37:30</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:37:35</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:37:56</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh']</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:38:02</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:38:08</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:38:28</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh'] | [start_month] 'January' not found in #startMonthId. Available (9): ['April', 'May', 'June', 'July', 'August', 'September', 'October', 'November', 'December']</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:38:49</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>[start_month] 'February' not found in #startMonthId. Available (9): ['April', 'May', 'June', 'July', 'August', 'September', 'October', 'November', 'December']</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:39:08</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>[activity_nature] 'New/Fresh' not found in #workTypId. Available (1): ['Operational']</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:39:31</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh'] | [start_month] 'April' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:39:54</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>[start_month] 'May' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:40:21</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>[start_month] 'June' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:40:44</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh'] | [start_month] 'July' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:41:07</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>[start_month] 'August' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:41:30</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>[start_month] 'September' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Success Rate</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Execution Time (s)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>643.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Completed At</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29 16:41:30</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00ED7D31"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ED7D31"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,10 +107,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,7 +119,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -632,97 +629,97 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activities realted to Record keeping /Maintainance of data base</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maintenance of community system</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-100</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>July</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -732,7 +729,7 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29 16:37:26</t>
+          <t>2026-06-29 17:41:19</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr"/>
@@ -740,97 +737,97 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 5 - Clean and Green Village</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness generation for use of natural products in daily life</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Social forestry and farm forestry</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-101</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>August</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -840,7 +837,7 @@
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29 16:37:30</t>
+          <t>2026-06-29 17:41:25</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr"/>
@@ -848,97 +845,97 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness camp on behavioural issues of Mission LiFE</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whether Training for Disaster Management conducted</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>September</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>120</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -948,7 +945,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29 16:37:35</t>
+          <t>2026-06-29 17:41:30</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
@@ -956,209 +953,205 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness campaign on SHG-PRI Convergence</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>October</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>130</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:37:56</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh']</t>
-        </is>
-      </c>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:41:36</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 4 - Water Sufficient Village</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amrit Sarovar/Pond/Farm Pond</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Drinking water</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 5</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>November</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1168,7 +1161,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29 16:38:02</t>
+          <t>2026-06-29 17:41:41</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
@@ -1176,97 +1169,97 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>December</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>150</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1276,7 +1269,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29 16:38:08</t>
+          <t>2026-06-29 17:41:46</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
@@ -1284,1010 +1277,974 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness Campaign  pension</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welfare of the weaker sections</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 7</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>April</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:38:28</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh'] | [start_month] 'January' not found in #startMonthId. Available (9): ['April', 'May', 'June', 'July', 'August', 'September', 'October', 'November', 'December']</t>
-        </is>
-      </c>
+          <t>110000</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:41:51</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness on Public Services/ Service Delivery Provisions/ RTI</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-107</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>April</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>170</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:38:49</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>[start_month] 'February' not found in #startMonthId. Available (9): ['April', 'May', 'June', 'July', 'August', 'September', 'October', 'November', 'December']</t>
-        </is>
-      </c>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:41:57</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Annual Expenses - Water Charges, Postal, Electricity Bills, Internet Bill, Printing Charges</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Maintenance of community system</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 9</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>March</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:39:08</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>[activity_nature] 'New/Fresh' not found in #workTypId. Available (1): ['Operational']</t>
-        </is>
-      </c>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:02</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness on disaster preparedness and mitigation</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Poverty allevation programme</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 10</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:39:31</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh'] | [start_month] 'April' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
-        </is>
-      </c>
+          <t>140000</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:08</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness on inclusion of beneficiaries under different scheme</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-110</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:39:54</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>[start_month] 'May' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
-        </is>
-      </c>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:15</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Awareness Campaign on services of ICDS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women and child development</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>210</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:40:21</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>[start_month] 'June' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
-        </is>
-      </c>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:20</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capacity Building &amp; Training of Elected Representatives &amp; Functionaries</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 13</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:40:44</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>[activity_nature] 'Maintenance' not found in #workTypId. Available (1): ['New/Fresh'] | [start_month] 'July' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
-        </is>
-      </c>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:26</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 9 - Women Friendly Village</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Access to Maternal Benefits</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women and child development</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:41:07</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>[start_month] 'August' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
-        </is>
-      </c>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:32</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charages / Fees and other activites for ISO Certification</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GP Office Infrastructure</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sample activity description for record 15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PDI-114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Women,Youth</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:41:30</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>[start_month] 'September' not found in #startMonthId. Available (3): ['January', 'February', 'March']</t>
-        </is>
-      </c>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:40</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2308,86 +2265,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Success Rate</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Execution Time (s)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>643.1</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>164.6</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Completed At</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-29 16:41:30</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29 17:42:40</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="eGram Activity Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Activities" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Automation_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,10 +116,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,140 +487,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="35" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>activity_key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>theme</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>activity_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>focus_area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>activity_type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>activity_description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pdi_indicator</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>activity_for</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>targeted_populace</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>activity_nature</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_directly_funded_by_panchayat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>estimated_completion_year</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>estimated_completion_month</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>estimated_completion_days</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>start_year</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>start_month</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>expected_beneficiary_general</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>expected_beneficiary_sc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>expected_beneficiary_st</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>indicative_unit_cost</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>total_indicative_cost</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>expected_results</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>flagship_scheme</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>select_supported_department</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>estimated_total_cost</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>shareable</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>major_head_choice</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>minor_head_choice</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>operation_type</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>operation_remarks</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>activity_output_type</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>final_action</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>processed_time</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>error_message</t>
         </is>
@@ -629,114 +707,155 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+          <t>ACT-0001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Annual Expenses - Water Charges, Postal, Electricity Bills, Internet Bill, Printing Charges</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Maintenance of community system</t>
+          <t>Awareness camp on behavioural issues of Mission LiFE</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Community Works</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sample activity description for record 9</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PDI-108</t>
+          <t>Awareness camp on behavioural issues of Mission LiFE</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Neonatal mortality rate (per 1,000 live births)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Women,Youth</t>
-        </is>
-      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>All</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>New/Fresh</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Okay</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>ARI Division Schemes: Coir Udyami Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Food &amp; Public Distribution</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-30 18:20:47</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>[validation] Please check atlest one Mission Antyodyaya(MA) Gap(s)</t>
-        </is>
-      </c>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07 17:03:10</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -788,7 +907,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -800,7 +919,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -812,7 +931,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -824,7 +943,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>87.3</t>
         </is>
       </c>
     </row>
@@ -836,7 +955,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30 18:20:48</t>
+          <t>2026-07-07 17:03:10</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -852,7 +852,7 @@
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07 17:03:10</t>
+          <t>2026-07-07 17:42:29</t>
         </is>
       </c>
       <c r="AI2" s="3" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>80.0</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07 17:03:10</t>
+          <t>2026-07-07 17:42:30</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -852,7 +852,7 @@
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07 17:42:29</t>
+          <t>2026-07-09 12:13:30</t>
         </is>
       </c>
       <c r="AI2" s="3" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.2</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07 17:42:30</t>
+          <t>2026-07-09 12:13:31</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,10 +116,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -496,35 +496,36 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
-    <col width="35" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
     <col width="24" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
-    <col width="22" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
-    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="30" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="60" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -560,145 +561,150 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>vprp_plan</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>pdi_indicator</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>activity_for</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>targeted_populace</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>activity_nature</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_directly_funded_by_panchayat</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>estimated_completion_year</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>estimated_completion_month</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>estimated_completion_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>start_year</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>start_month</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>expected_beneficiary_general</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>expected_beneficiary_sc</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>expected_beneficiary_st</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>indicative_unit_cost</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>total_indicative_cost</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>expected_results</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>flagship_scheme</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>select_supported_department</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>estimated_total_cost</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>shareable</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>major_head_choice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>minor_head_choice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>operation_type</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>operation_remarks</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>activity_output_type</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>final_action</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>processed_time</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>error_message</t>
         </is>
@@ -707,155 +713,302 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0001</t>
+          <t>ACT-0070</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 2 - Healthy Village</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Awareness camp on behavioural issues of Mission LiFE</t>
+          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Beneficiary Oriented Programmes</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Awareness camp on behavioural issues of Mission LiFE</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Neonatal mortality rate (per 1,000 live births)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>New/Fresh</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>April</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>ARI Division Schemes: Coir Udyami Yojana - Center Scheme</t>
+          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Department of Food &amp; Public Distribution</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
+          <t>Pradhan Mantri Krishi Sinchayee Yojana (PMKSY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>Whether the activity is for Elementary/Primary Education</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>Training/Capacity Building</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Save and Forward</t>
         </is>
       </c>
-      <c r="AG2" s="3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09 12:13:30</t>
-        </is>
-      </c>
-      <c r="AI2" s="3" t="inlineStr"/>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:59:58</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Training modal did not open: showTrainingDetailsPopup; diagnostics={'modalExists': True, 'modalClass': 'modal fade', 'modalDisplay': 'none', 'modalVisibility': 'visible', 'modalAriaHidden': None, 'radioExists': True, 'radioChecked': True, 'radioDisabled': False, 'radioOnclick': "return showAssetDetailsPopup('addassetdtlsDiv102',this.id);", 'outputTypeHidden': '', 'startMonthValue': '4', 'totalIndicativeCostValue': '192', 'totalExpectedBeneficiariesValue': '24', 'trainingCategoryVisible': False, 'hasModalBackdrop': False, 'visibleErrors': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0081</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Theme 3 - Child Friendly Village</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Women and child development</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>National Health Mission (NHM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>Whether the activity is for Elementary/Primary Education</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 01:00:35</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Training modal did not open: showTrainingDetailsPopup; diagnostics={'modalExists': True, 'modalClass': 'modal fade', 'modalDisplay': 'none', 'modalVisibility': 'visible', 'modalAriaHidden': None, 'radioExists': True, 'radioChecked': True, 'radioDisabled': False, 'radioOnclick': "return showAssetDetailsPopup('addassetdtlsDiv102',this.id);", 'outputTypeHidden': '', 'startMonthValue': '4', 'totalIndicativeCostValue': '80', 'totalExpectedBeneficiariesValue': '10', 'trainingCategoryVisible': False, 'hasModalBackdrop': False, 'visibleErrors': []}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -895,7 +1048,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -907,7 +1060,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -919,7 +1072,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -931,7 +1084,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -943,7 +1096,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>165.9</t>
         </is>
       </c>
     </row>
@@ -955,7 +1108,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09 12:13:31</t>
+          <t>2026-08-28 01:00:35</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,10 +116,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,22 +713,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0070</t>
+          <t>ACT-0028</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 3 - Child Friendly Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Poverty allevation programme</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -790,48 +790,44 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>135</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Pradhan Mantri Krishi Sinchayee Yojana (PMKSY) - Center Scheme</t>
+          <t>Matsaya Yojna - Center Scheme</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>Whether the activity is for Elementary/Primary Education</t>
-        </is>
-      </c>
+      <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr"/>
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="inlineStr">
@@ -846,169 +842,15 @@
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 00:59:58</t>
-        </is>
-      </c>
-      <c r="AJ2" s="3" t="inlineStr">
-        <is>
-          <t>[activity_output] Training modal did not open: showTrainingDetailsPopup; diagnostics={'modalExists': True, 'modalClass': 'modal fade', 'modalDisplay': 'none', 'modalVisibility': 'visible', 'modalAriaHidden': None, 'radioExists': True, 'radioChecked': True, 'radioDisabled': False, 'radioOnclick': "return showAssetDetailsPopup('addassetdtlsDiv102',this.id);", 'outputTypeHidden': '', 'startMonthValue': '4', 'totalIndicativeCostValue': '192', 'totalExpectedBeneficiariesValue': '24', 'trainingCategoryVisible': False, 'hasModalBackdrop': False, 'visibleErrors': []}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ACT-0081</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Theme 3 - Child Friendly Village</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Women and child development</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Community Works</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>New/Fresh</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>National Health Mission (NHM) - Center Scheme</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>Whether the activity is for Elementary/Primary Education</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>Training/Capacity Building</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t>Save and Forward</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28 01:00:35</t>
-        </is>
-      </c>
-      <c r="AJ3" s="3" t="inlineStr">
-        <is>
-          <t>[activity_output] Training modal did not open: showTrainingDetailsPopup; diagnostics={'modalExists': True, 'modalClass': 'modal fade', 'modalDisplay': 'none', 'modalVisibility': 'visible', 'modalAriaHidden': None, 'radioExists': True, 'radioChecked': True, 'radioDisabled': False, 'radioOnclick': "return showAssetDetailsPopup('addassetdtlsDiv102',this.id);", 'outputTypeHidden': '', 'startMonthValue': '4', 'totalIndicativeCostValue': '80', 'totalExpectedBeneficiariesValue': '10', 'trainingCategoryVisible': False, 'hasModalBackdrop': False, 'visibleErrors': []}</t>
-        </is>
-      </c>
+          <t>2026-08-28 22:05:23</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1048,7 +890,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1060,7 +902,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1072,7 +914,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +926,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1096,7 +938,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>165.9</t>
+          <t>77.8</t>
         </is>
       </c>
     </row>
@@ -1108,7 +950,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28 01:00:35</t>
+          <t>2026-08-28 22:05:24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ED7D31"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00ED7D31"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,7 +107,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,7 +122,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,22 +716,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0028</t>
+          <t>ACT-0280</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Poverty allevation programme</t>
+          <t>Welfare of the weaker sections</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -738,10 +741,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -790,12 +797,12 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -805,25 +812,29 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Matsaya Yojna - Center Scheme</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr"/>
+          <t>Mahatma Gandhi National Rural Employment Guarantee Scheme (MGNREGS) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Food &amp; Public Distribution</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
@@ -847,10 +858,3080 @@
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:05:23</t>
+          <t>2026-08-28 22:30:32</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0281</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign about UDID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign about UDID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign about UDID</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Grameen Kaushalya Yojana(DDUGKY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>Department of Health &amp; Family Welfare</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:31:12</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0282</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on Scheme related to pension</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on Scheme related to pension</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on Scheme related to pension</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>National Social Assistance Programme (NSAP) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Women and Child Development</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:31:38</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0283</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on different social protection scheme</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on different social protection scheme</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on different social protection scheme</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri AwasYojana Gramin PMAY (G) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Power</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:32:22</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0284</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Swachh Bharat Mission (Gramin) (SBM (G)] - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:32:31</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0285</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Jal Jeevan Mission (JJM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:32:41</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0286</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Gram Jyoti Yojana (DDUGJY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>Department of Rural Development</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:33:06</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0287</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Krishi Sinchayee Yojana (PMKSY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>Department of Drinking Water and Sanitation</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:33:31</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0288</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>National Health Mission (NHM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>Department of Health &amp; Family Welfare</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:34:12</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0289</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Day Meal Scheme (MDM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:34:22</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0290</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Matru Vandana Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:34:32</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0291</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Ujjwala Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>Department of Rural Development</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:34:44</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0292</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Witch Hunting (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Witch Hunting (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Witch Hunting (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Antodaya Anna Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:35:08</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0001</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Samagara Shikha Abhiyan - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:35:19</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0002</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Poshan Abhiyan/ICDS - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:35:59</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0003</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Animal husbandry</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Beti Bachao Beti Padao - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:36:09</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0015</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>National Rural Livelihood Mission (NRLM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:36:34</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0020</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Technical training and vocational education</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Beneficiary Oriented Programmes</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Pashudhan Scheme - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:37:15</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0028</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Matsaya Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:37:25</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0036</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Janani Surakha Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:37:46</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
+        <is>
+          <t>[activity_output] Training modal did not open: showTrainingDetailsPopup; diagnostics={'modalExists': True, 'modalClass': 'modal fade', 'modalDisplay': 'none', 'modalVisibility': 'visible', 'modalAriaHidden': None, 'radioExists': True, 'radioChecked': True, 'radioDisabled': False, 'radioOnclick': "return showAssetDetailsPopup('addassetdtlsDiv102',this.id);", 'outputTypeHidden': '', 'startMonthValue': '', 'totalIndicativeCostValue': '117', 'totalExpectedBeneficiariesValue': '13', 'trainingCategoryVisible': False, 'hasModalBackdrop': False, 'visibleErrors': ['Please select start Month']}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0037</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Ayushman Bharat - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:37:57</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0043</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>National Biogas and Manure Management Programme - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:38:38</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -871,86 +3952,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Success Rate</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>95.5%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Execution Time (s)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>77.8</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>506.1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Completed At</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:05:24</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:38:38</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00ED7D31"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ED7D31"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,10 +107,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,7 +119,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -716,22 +713,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0280</t>
+          <t>ACT-0306</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
+          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Welfare of the weaker sections</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -741,14 +738,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -802,7 +795,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -812,17 +805,17 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>153</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
+          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
@@ -830,11 +823,7 @@
           <t>Mahatma Gandhi National Rural Employment Guarantee Scheme (MGNREGS) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>Department of Food &amp; Public Distribution</t>
-        </is>
-      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
@@ -858,7 +847,7 @@
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:30:32</t>
+          <t>2026-08-29 20:06:27</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr"/>
@@ -866,22 +855,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ACT-0281</t>
+          <t>ACT-0310</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign about UDID</t>
+          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Adult and non-formal education</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -891,7 +880,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign about UDID</t>
+          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -943,32 +932,32 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign about UDID</t>
+          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -976,11 +965,7 @@
           <t>Deendayal Upadhyaya Grameen Kaushalya Yojana(DDUGKY) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>Department of Health &amp; Family Welfare</t>
-        </is>
-      </c>
+      <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
@@ -1004,7 +989,7 @@
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:31:12</t>
+          <t>2026-08-29 20:06:38</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1012,17 +997,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ACT-0282</t>
+          <t>ACT-0313</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign on Scheme related to pension</t>
+          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1037,14 +1022,10 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign on Scheme related to pension</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -1093,32 +1074,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign on Scheme related to pension</t>
+          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -1126,11 +1107,7 @@
           <t>National Social Assistance Programme (NSAP) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>Ministry of Women and Child Development</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
@@ -1154,7 +1131,7 @@
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:31:38</t>
+          <t>2026-08-29 20:06:48</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
@@ -1162,22 +1139,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ACT-0283</t>
+          <t>ACT-0314</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign on different social protection scheme</t>
+          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Adult and non-formal education</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1187,7 +1164,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign on different social protection scheme</t>
+          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -1239,32 +1216,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>34</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Awareness Campaign on different social protection scheme</t>
+          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -1272,11 +1249,7 @@
           <t>Pradhan Mantri AwasYojana Gramin PMAY (G) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>Ministry of Power</t>
-        </is>
-      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr"/>
@@ -1300,7 +1273,7 @@
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:32:22</t>
+          <t>2026-08-29 20:06:58</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1308,22 +1281,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ACT-0284</t>
+          <t>ACT-0315</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Adult and non-formal education</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1333,14 +1306,10 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -1389,32 +1358,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>160</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1446,7 +1415,7 @@
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:32:31</t>
+          <t>2026-08-29 20:07:10</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
@@ -1454,22 +1423,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ACT-0285</t>
+          <t>ACT-0317</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Poverty allevation programme</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1479,14 +1448,10 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -1535,32 +1500,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>26</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
@@ -1592,7 +1557,7 @@
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:32:41</t>
+          <t>2026-08-29 20:07:52</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
@@ -1600,17 +1565,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ACT-0286</t>
+          <t>ACT-0001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1625,14 +1590,10 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1681,32 +1642,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -1714,11 +1675,7 @@
           <t>Deendayal Upadhyaya Gram Jyoti Yojana (DDUGJY) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>Department of Rural Development</t>
-        </is>
-      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="inlineStr"/>
       <c r="AB8" s="2" t="inlineStr"/>
@@ -1742,7 +1699,7 @@
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:33:06</t>
+          <t>2026-08-29 20:08:34</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
@@ -1750,22 +1707,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ACT-0287</t>
+          <t>ACT-0002</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1775,14 +1732,10 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1831,32 +1784,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1864,11 +1817,7 @@
           <t>Pradhan Mantri Krishi Sinchayee Yojana (PMKSY) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>Department of Drinking Water and Sanitation</t>
-        </is>
-      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
@@ -1892,7 +1841,7 @@
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:33:31</t>
+          <t>2026-08-29 20:09:15</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
@@ -1900,22 +1849,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ACT-0288</t>
+          <t>ACT-0003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Animal husbandry</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1925,7 +1874,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1981,32 +1930,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -2014,11 +1963,7 @@
           <t>National Health Mission (NHM) - Center Scheme</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>Department of Health &amp; Family Welfare</t>
-        </is>
-      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
@@ -2042,7 +1987,7 @@
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:34:12</t>
+          <t>2026-08-29 20:09:57</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr"/>
@@ -2050,22 +1995,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ACT-0289</t>
+          <t>ACT-0015</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Poverty allevation programme</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2075,14 +2020,10 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -2131,32 +2072,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -2188,7 +2129,7 @@
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:34:22</t>
+          <t>2026-08-29 20:10:38</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr"/>
@@ -2196,32 +2137,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ACT-0290</t>
+          <t>ACT-0020</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+          <t>Facilitation/provision of skill development training</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Technical training and vocational education</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Community Works</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+          <t>Facilitation/provision of skill development training</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2277,32 +2218,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>69</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+          <t>Facilitation/provision of skill development training</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -2334,7 +2275,7 @@
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:34:32</t>
+          <t>2026-08-29 20:11:19</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr"/>
@@ -2342,22 +2283,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ACT-0291</t>
+          <t>ACT-0028</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Poverty allevation programme</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2367,14 +2308,10 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2423,32 +2360,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>150</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2456,11 +2393,7 @@
           <t>Pradhan Mantri Ujjwala Yojana - Center Scheme</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>Department of Rural Development</t>
-        </is>
-      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr"/>
@@ -2484,7 +2417,7 @@
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:34:44</t>
+          <t>2026-08-29 20:11:30</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr"/>
@@ -2492,22 +2425,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ACT-0292</t>
+          <t>ACT-0036</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Witch Hunting (Social exclusion)</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2517,14 +2450,10 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Witch Hunting (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2573,32 +2502,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Witch Hunting (Social exclusion)</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2630,7 +2559,7 @@
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:35:08</t>
+          <t>2026-08-29 20:11:41</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr"/>
@@ -2638,22 +2567,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ACT-0001</t>
+          <t>ACT-0037</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2663,10 +2592,14 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -2715,7 +2648,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2725,22 +2658,22 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>42</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2772,7 +2705,7 @@
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:35:19</t>
+          <t>2026-08-29 20:11:51</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr"/>
@@ -2780,22 +2713,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ACT-0002</t>
+          <t>ACT-0043</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Family welfare</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2805,10 +2738,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -2857,32 +2794,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>96</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2914,7 +2851,7 @@
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:35:59</t>
+          <t>2026-08-29 20:12:32</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr"/>
@@ -2922,39 +2859,35 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ACT-0003</t>
+          <t>ACT-0044</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Animal husbandry</t>
+          <t>Family welfare</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Community Works</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -3003,17 +2936,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -3023,12 +2956,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>77</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
@@ -3060,7 +2993,7 @@
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:36:09</t>
+          <t>2026-08-29 20:12:58</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr"/>
@@ -3068,22 +3001,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACT-0015</t>
+          <t>ACT-0046</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Poverty allevation programme</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3093,7 +3026,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+          <t>Organize Mental Health Awareness Camps &amp; Development of IEC materials on Mental Health</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -3145,32 +3078,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>84</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -3202,7 +3135,7 @@
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:36:34</t>
+          <t>2026-08-29 20:13:23</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr"/>
@@ -3210,39 +3143,35 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ACT-0020</t>
+          <t>ACT-0047</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Facilitation/provision of skill development training</t>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Technical training and vocational education</t>
+          <t>Family welfare</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Beneficiary Oriented Programmes</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Facilitation/provision of skill development training</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -3291,12 +3220,12 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -3306,17 +3235,17 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>84</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>Facilitation/provision of skill development training</t>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -3348,7 +3277,7 @@
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:37:15</t>
+          <t>2026-08-29 20:14:04</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr"/>
@@ -3356,22 +3285,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ACT-0028</t>
+          <t>ACT-0048</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 2 - Healthy Village</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Poverty allevation programme</t>
+          <t>Cultural activities</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3381,10 +3310,14 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -3433,32 +3366,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>27</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3490,7 +3423,7 @@
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:37:25</t>
+          <t>2026-08-29 20:14:14</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr"/>
@@ -3498,7 +3431,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ACT-0036</t>
+          <t>ACT-0051</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3508,7 +3441,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+          <t>Organizing awareness camp about child heath through campaign</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3523,7 +3456,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+          <t>Organizing awareness camp about child heath through campaign</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -3575,32 +3508,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>144</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+          <t>Organizing awareness camp about child heath through campaign</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -3625,26 +3558,22 @@
           <t>Save and Forward</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:37:46</t>
-        </is>
-      </c>
-      <c r="AJ21" s="4" t="inlineStr">
-        <is>
-          <t>[activity_output] Training modal did not open: showTrainingDetailsPopup; diagnostics={'modalExists': True, 'modalClass': 'modal fade', 'modalDisplay': 'none', 'modalVisibility': 'visible', 'modalAriaHidden': None, 'radioExists': True, 'radioChecked': True, 'radioDisabled': False, 'radioOnclick': "return showAssetDetailsPopup('addassetdtlsDiv102',this.id);", 'outputTypeHidden': '', 'startMonthValue': '', 'totalIndicativeCostValue': '117', 'totalExpectedBeneficiariesValue': '13', 'trainingCategoryVisible': False, 'hasModalBackdrop': False, 'visibleErrors': ['Please select start Month']}</t>
-        </is>
-      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 20:14:39</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ACT-0037</t>
+          <t>ACT-0052</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3654,12 +3583,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Family welfare</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3669,14 +3598,10 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -3725,19 +3650,19 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -3745,12 +3670,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3782,7 +3707,7 @@
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:37:57</t>
+          <t>2026-08-29 20:15:19</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr"/>
@@ -3790,7 +3715,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ACT-0043</t>
+          <t>ACT-0053</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3800,7 +3725,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+          <t>Organizing awareness camp on rountine immunization of children</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3815,14 +3740,10 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Organizing awareness camp on rountine immunization of children</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -3871,32 +3792,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+          <t>Organizing awareness camp on rountine immunization of children</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
@@ -3928,7 +3849,7 @@
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 22:38:38</t>
+          <t>2026-08-29 20:16:01</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr"/>
@@ -3952,86 +3873,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Total Records</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>21</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Success Rate</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>95.5%</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Execution Time (s)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>506.1</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>587.8</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Completed At</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:38:38</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-29 20:16:01</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -713,22 +713,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0306</t>
+          <t>ACT-0063</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 8 - Village with Good Governance</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
+          <t>Awareness Campaign on services of ICDS: Child rights &amp; protection</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Women and child development</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
+          <t>Awareness Campaign on services of ICDS: Child rights &amp; protection</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -795,12 +795,12 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>162</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
+          <t>Awareness Campaign on services of ICDS: Child rights &amp; protection</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:06:27</t>
+          <t>2026-08-30 14:34:37</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr"/>
@@ -855,22 +855,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ACT-0310</t>
+          <t>ACT-0064</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Theme 8 - Village with Good Governance</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
+          <t>Awareness Program/ Rallies / Street Play on child marriage, child labour, child marriage, trafficking</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Adult and non-formal education</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -880,10 +880,14 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Awareness Program/ Rallies / Street Play on child marriage, child labour, child marriage, trafficking</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -932,32 +936,32 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>72</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
+          <t>Awareness Program/ Rallies / Street Play on child marriage, child labour, child marriage, trafficking</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:06:38</t>
+          <t>2026-08-30 14:34:47</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -997,22 +1001,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ACT-0313</t>
+          <t>ACT-0065</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Theme 8 - Village with Good Governance</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
+          <t>Awareness Program/ Rallies/ Campaign on importance of education/ vocational / technical education</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1022,10 +1026,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Awareness Program/ Rallies/ Campaign on importance of education/ vocational / technical education</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -1074,32 +1082,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>39</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
+          <t>Awareness Program/ Rallies/ Campaign on importance of education/ vocational / technical education</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -1131,7 +1139,7 @@
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:06:48</t>
+          <t>2026-08-30 14:36:29</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
@@ -1139,22 +1147,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ACT-0314</t>
+          <t>ACT-0066</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Theme 8 - Village with Good Governance</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
+          <t>Awareness Program/Campaign - Health, Nutrion &amp; Hygiene  practices</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Adult and non-formal education</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1164,7 +1172,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
+          <t>Awareness Program/Campaign - Health, Nutrion &amp; Hygiene practices</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -1216,32 +1224,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>138</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
+          <t>Awareness Program/Campaign - Health, Nutrion &amp; Hygiene  practices</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -1273,7 +1281,7 @@
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:06:58</t>
+          <t>2026-08-30 14:37:10</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1281,22 +1289,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ACT-0315</t>
+          <t>ACT-0067</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Theme 8 - Village with Good Governance</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+          <t>Awareness camp on different schemes related to special children</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Adult and non-formal education</t>
+          <t>Women and child development</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1306,7 +1314,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+          <t>Awareness camp on different schemes related to special children</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -1358,32 +1366,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+          <t>Awareness camp on different schemes related to special children</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1415,7 +1423,7 @@
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:07:10</t>
+          <t>2026-08-30 14:37:20</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
@@ -1423,22 +1431,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ACT-0317</t>
+          <t>ACT-0068</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Theme 8 - Village with Good Governance</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+          <t>Awareness on gender discrimination and gender equality</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Women and child development</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1448,7 +1456,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+          <t>Awareness on gender discrimination and gender equality</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -1500,32 +1508,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>161</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+          <t>Awareness on gender discrimination and gender equality</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
@@ -1557,7 +1565,7 @@
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:07:52</t>
+          <t>2026-08-30 14:37:31</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
@@ -1565,22 +1573,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ACT-0001</t>
+          <t>ACT-0069</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+          <t>Capacity Building &amp; Training of Children</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Social welfare</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1590,7 +1598,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
+          <t>Capacity Building &amp; Training of Children</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1642,32 +1650,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>152</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+          <t>Capacity Building &amp; Training of Children</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -1699,7 +1707,7 @@
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:08:34</t>
+          <t>2026-08-30 14:38:11</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
@@ -1707,22 +1715,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ACT-0002</t>
+          <t>ACT-0070</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1732,7 +1740,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1784,32 +1792,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>27</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+          <t>Child Participation, Leadership Strengthening &amp; Facilitation</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1821,7 +1829,11 @@
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>Whether the activity is for Elementary/Primary Education</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr">
@@ -1841,7 +1853,7 @@
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:09:15</t>
+          <t>2026-08-30 14:38:53</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
@@ -1849,22 +1861,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ACT-0003</t>
+          <t>ACT-0081</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Animal husbandry</t>
+          <t>Women and child development</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1874,14 +1886,10 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1930,17 +1938,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1950,12 +1958,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+          <t>Institutional Strengthening &amp; Convergence on child related issues</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1967,7 +1975,11 @@
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>Whether the activity is for Elementary/Primary Education</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr"/>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr">
@@ -1987,7 +1999,7 @@
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:09:57</t>
+          <t>2026-08-30 14:39:05</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr"/>
@@ -1995,22 +2007,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ACT-0015</t>
+          <t>ACT-0087</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+          <t>Theme 3 - Child Friendly Village</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+          <t>Providing Educational Materials /Special Coaching Support to the student</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Poverty allevation programme</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2020,7 +2032,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+          <t>Providing Educational Materials /Special Coaching Support to the student</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -2072,32 +2084,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+          <t>Providing Educational Materials /Special Coaching Support to the student</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -2129,7 +2141,7 @@
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:10:38</t>
+          <t>2026-08-30 14:39:16</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr"/>
@@ -2137,7 +2149,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ACT-0020</t>
+          <t>ACT-0001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2147,29 +2159,25 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Facilitation/provision of skill development training</t>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Technical training and vocational education</t>
+          <t>Social welfare</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Beneficiary Oriented Programmes</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Facilitation/provision of skill development training</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -2218,7 +2226,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -2228,22 +2236,22 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>54</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>Facilitation/provision of skill development training</t>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -2275,7 +2283,7 @@
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:11:19</t>
+          <t>2026-08-30 14:39:58</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr"/>
@@ -2283,7 +2291,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ACT-0028</t>
+          <t>ACT-0002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2293,12 +2301,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Poverty allevation programme</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2308,7 +2316,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -2360,32 +2368,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>102</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2417,7 +2425,7 @@
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:11:30</t>
+          <t>2026-08-30 14:40:10</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr"/>
@@ -2425,22 +2433,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ACT-0036</t>
+          <t>ACT-0003</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Theme 2 - Healthy Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Animal husbandry</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2450,10 +2458,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2507,27 +2519,27 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>48</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2559,7 +2571,7 @@
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:11:41</t>
+          <t>2026-08-30 14:40:52</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr"/>
@@ -2567,22 +2579,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ACT-0037</t>
+          <t>ACT-0015</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Theme 2 - Healthy Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Poverty allevation programme</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2592,14 +2604,10 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -2648,32 +2656,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>68</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2705,7 +2713,7 @@
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:11:51</t>
+          <t>2026-08-30 14:41:02</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr"/>
@@ -2713,32 +2721,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ACT-0043</t>
+          <t>ACT-0020</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Theme 2 - Healthy Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+          <t>Facilitation/provision of skill development training</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Family welfare</t>
+          <t>Technical training and vocational education</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Community Works</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+          <t>Facilitation/provision of skill development training</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2794,32 +2802,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+          <t>Facilitation/provision of skill development training</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2851,7 +2859,7 @@
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:12:32</t>
+          <t>2026-08-30 14:41:12</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr"/>
@@ -2859,32 +2867,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ACT-0044</t>
+          <t>ACT-0028</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Theme 2 - Healthy Village</t>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Family welfare</t>
+          <t>Poverty allevation programme</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Beneficiary Oriented Programmes</t>
+          <t>Community Works</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -2936,17 +2944,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2956,12 +2964,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>140</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
@@ -2993,7 +3001,7 @@
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:12:58</t>
+          <t>2026-08-30 14:41:22</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr"/>
@@ -3001,7 +3009,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ACT-0046</t>
+          <t>ACT-0036</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3011,7 +3019,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3026,7 +3034,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Organize Mental Health Awareness Camps &amp; Development of IEC materials on Mental Health</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -3078,32 +3086,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>91</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -3135,7 +3143,7 @@
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:13:23</t>
+          <t>2026-08-30 14:41:32</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr"/>
@@ -3143,7 +3151,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ACT-0047</t>
+          <t>ACT-0037</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3153,12 +3161,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Family welfare</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3168,10 +3176,14 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -3220,32 +3232,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -3277,7 +3289,7 @@
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:14:04</t>
+          <t>2026-08-30 14:41:42</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr"/>
@@ -3285,7 +3297,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ACT-0048</t>
+          <t>ACT-0043</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -3295,12 +3307,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Cultural activities</t>
+          <t>Family welfare</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3310,7 +3322,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3366,12 +3378,12 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -3381,17 +3393,17 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>153</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3423,7 +3435,7 @@
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:14:14</t>
+          <t>2026-08-30 14:42:23</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr"/>
@@ -3431,7 +3443,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ACT-0051</t>
+          <t>ACT-0044</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -3441,22 +3453,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp about child heath through campaign</t>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Family welfare</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Community Works</t>
+          <t>Beneficiary Oriented Programmes</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp about child heath through campaign</t>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -3508,32 +3520,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp about child heath through campaign</t>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -3565,7 +3577,7 @@
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:14:39</t>
+          <t>2026-08-30 14:42:34</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr"/>
@@ -3573,7 +3585,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ACT-0052</t>
+          <t>ACT-0046</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -3583,12 +3595,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Family welfare</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3598,7 +3610,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+          <t>Organize Mental Health Awareness Camps &amp; Development of IEC materials on Mental Health</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -3650,12 +3662,12 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -3665,17 +3677,17 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3707,7 +3719,7 @@
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:15:19</t>
+          <t>2026-08-30 14:42:44</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr"/>
@@ -3715,7 +3727,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ACT-0053</t>
+          <t>ACT-0047</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3725,7 +3737,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp on rountine immunization of children</t>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3740,7 +3752,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp on rountine immunization of children</t>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -3792,32 +3804,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>Organizing awareness camp on rountine immunization of children</t>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
@@ -3849,7 +3861,7 @@
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:16:01</t>
+          <t>2026-08-30 14:42:54</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr"/>
@@ -3940,7 +3952,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>587.8</t>
+          <t>520.7</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3964,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-29 20:16:01</t>
+          <t>2026-08-30 14:42:54</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -851,24 +851,12 @@
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30 22:52:21</t>
+          <t>2026-08-30 23:19:50</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[activity_output] Locator.check: Clicking the checkbox did not change its state
-Call log:
-  - waiting for locator("input#assetCovgeAreaId, input[name='assetDetails.astCvrgCd'][value='A']").first
-    - locator resolved to &lt;input value="A" type="radio" id="assetCovgeAreaId" name="assetDetails.astCvrgCd" onclick="showVillageForGPList(this.value)"/&gt;
-  - attempting click action
-    - scrolling into view if needed
-    - done scrolling
-    - forcing action
-    - performing click action
-    - click action done
-    - waiting for scheduled navigations to finish
-    - navigations have finished
-</t>
+          <t>[activity_output] Page.wait_for_function() takes 2 positional arguments but 3 positional arguments (and 1 keyword-only argument) were given</t>
         </is>
       </c>
     </row>
@@ -958,7 +946,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>12.3</t>
         </is>
       </c>
     </row>
@@ -970,7 +958,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30 22:52:21</t>
+          <t>2026-08-30 23:19:50</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,22 +713,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0122</t>
+          <t>ACT-0280</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 4 - Water Sufficient Village</t>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Creation of other water recharging structure/Recharge pit,shaft/Anicut/Check,Earthen,Percolation Dams/Continous Contour Trenches,Bunds/Drainage Pit</t>
+          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Water Conservation</t>
+          <t>Welfare of the weaker sections</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>chek dam</t>
+          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -794,41 +794,45 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Creation of other water recharging structure/Recharge pit,shaft/Anicut/Check,Earthen,Percolation Dams/Continous Contour Trenches,Bunds/Drainage Pit</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
+          <t>Awareness on Discrimination against SC/ST/PVTG/religious minority communities (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Mahatma Gandhi National Rural Employment Guarantee Scheme (MGNREGS) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Department of Food &amp; Public Distribution</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr"/>
@@ -836,7 +840,7 @@
       <c r="AE2" s="2" t="inlineStr"/>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Training/Capacity Building</t>
         </is>
       </c>
       <c r="AG2" s="2" t="inlineStr">
@@ -851,12 +855,3162 @@
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30 23:19:50</t>
+          <t>2026-08-31 11:08:45</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t>[activity_output] Page.wait_for_function() takes 2 positional arguments but 3 positional arguments (and 1 keyword-only argument) were given</t>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0281</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign about UDID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign about UDID</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign about UDID</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Grameen Kaushalya Yojana(DDUGKY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>Department of Health &amp; Family Welfare</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:09:22</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0282</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on Scheme related to pension</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on Scheme related to pension</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on Scheme related to pension</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>National Social Assistance Programme (NSAP) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Women and Child Development</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:09:45</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0283</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on different social protection scheme</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on different social protection scheme</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Awareness Campaign on different social protection scheme</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri AwasYojana Gramin PMAY (G) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Power</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:10:07</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0284</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Discrimination against transgenders (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Swachh Bharat Mission (Gramin) (SBM (G)] - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:10:14</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0285</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to migrant labourers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Jal Jeevan Mission (JJM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:10:21</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0286</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to persons with disabilities (PWDs) (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Gram Jyoti Yojana (DDUGJY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>Department of Rural Development</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:10:59</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0287</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sanitation workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Krishi Sinchayee Yojana (PMKSY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>Department of Drinking Water and Sanitation</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:11:37</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0288</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to sex workers (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>National Health Mission (NHM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>Department of Health &amp; Family Welfare</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:11:59</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0289</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Day Meal Scheme (MDM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:12:06</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0290</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Issues related to the elderly (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Matru Vandana Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:12:28</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0291</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Lack of access to education for Persons with Disabilities (Inclusive Education)</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Ujjwala Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>Department of Rural Development</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:12:34</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0292</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Witch Hunting (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Witch Hunting (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Awareness on Witch Hunting (Social exclusion)</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Antodaya Anna Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:12:42</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0001</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Samagara Shikha Abhiyan - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:13:20</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0002</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Poshan Abhiyan/ICDS - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:13:42</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0003</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Animal husbandry</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Beti Bachao Beti Padao - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:14:05</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0015</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>National Rural Livelihood Mission (NRLM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:14:42</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0020</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Technical training and vocational education</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Beneficiary Oriented Programmes</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Pashudhan Scheme - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:15:20</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0028</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Matsaya Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:15:42</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0036</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Janani Surakha Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:15:49</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0037</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Ayushman Bharat - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:15:56</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0043</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>National Biogas and Manure Management Programme - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 11:16:33</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr">
+        <is>
+          <t>[activity_output] Page.eval_on_selector: Failed to find element matching selector "#trngLocCd"</t>
         </is>
       </c>
     </row>
@@ -898,7 +4052,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -922,7 +4076,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -946,7 +4100,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>485.7</t>
         </is>
       </c>
     </row>
@@ -958,7 +4112,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30 23:19:50</t>
+          <t>2026-08-31 11:16:33</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,17 +713,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACT-0289</t>
+          <t>ACT-0306</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Theme 7 - Socially Just and Socially Secured Village</t>
+          <t>Theme 8 - Village with Good Governance</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -738,14 +738,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -794,37 +790,37 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>130</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Awareness on Issues related to single women/widows (Social exclusion)</t>
+          <t>Capacity Building &amp; Training of Elected Representatives, Functionaries &amp; other stakeholders</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Mid-Day Meal Scheme (MDM) - Center Scheme</t>
+          <t>Mahatma Gandhi National Rural Employment Guarantee Scheme (MGNREGS) - Center Scheme</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
@@ -851,10 +847,5762 @@
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31 12:23:00</t>
+          <t>2026-09-01 01:08:08</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0307</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Theme 8 - Village with Good Governance</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Adult and non-formal education</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Cost for Disaster Readiness, relief and mitigation activities (Training, planning, survey etc)</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Grameen Kaushalya Yojana(DDUGKY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:09:19</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0308</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Theme 8 - Village with Good Governance</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness Campaign for active participation in Gram Sabha, Ward Sabha, Mahila Sabha</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>National Social Assistance Programme (NSAP) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:09:30</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0309</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Theme 8 - Village with Good Governance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Adult and non-formal education</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness campaign on SHG-PRI Convergence /Public Services/ Service Delivery Provisions/ RTI/Grivences</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri AwasYojana Gramin PMAY (G) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:09:55</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0310</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Theme 8 - Village with Good Governance</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Adult and non-formal education</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>IEC &amp; Awareness on disaster preparedness and mitigation</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Swachh Bharat Mission (Gramin) (SBM (G)] - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:10:36</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0311</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Theme 8 - Village with Good Governance</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Organising of Gram Sabha/ Ward Sabha/ Mahila Sabha/ GPDP</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Jal Jeevan Mission (JJM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:10:46</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0312</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Social welfare</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Conduct IEC/awareness and  inclusion camps for social protection and beneficiary-oriented schemes</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>Deendayal Upadhyaya Gram Jyoti Yojana (DDUGJY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:10:56</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0313</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on FPOs and support formation/strngthening of FPOs through farmer mobilisation</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Krishi Sinchayee Yojana (PMKSY) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:11:06</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0314</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Animal husbandry</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Create awareness on volunteering and community support initiatices, including animal welfare activities</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>National Health Mission (NHM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:11:17</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0315</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Facilitate formation oh SHGs and provide support for strengthening SHGs in Gram Panchayats</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Day Meal Scheme (MDM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:11:59</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0316</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Technical training and vocational education</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Beneficiary Oriented Programmes</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Facilitation/provision of skill development training</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Matru Vandana Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:12:09</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0317</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Theme 1 - Poverty Free and Enhanced Livelihoods Village</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Poverty allevation programme</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Organise career counselling camps to promote self-employment opportunities at the GP level</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Ujjwala Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:12:20</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0318</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of Vector Borne Diseases (VBD)</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Antodaya Anna Yojana - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:12:30</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0319</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness Progarm &amp; IEC campaign on symptoms of anaemia; vicious cycle of anaemia</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Samagara Shikha Abhiyan - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:12:40</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0320</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Oraginizing awareness camp/ program on significance of health &amp; nutrition</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Poshan Abhiyan/ICDS - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:12:51</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0321</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Beneficiary Oriented Programmes</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Oranizing Training of Mid Wives on safe &amp; institutional delivery</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Beti Bachao Beti Padao - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:13:32</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0322</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Organize Mental Health Awareness Camps &amp; Development of IEC materials on Mental Health</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Organize Mental Health Awareness Camps  &amp; Development of IEC materials on Mental Health</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>National Rural Livelihood Mission (NRLM) - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:14:14</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0323</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Organizing Awareness &amp; IEC campaign on Health Schemes/ Program</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Pashudhan Scheme - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:14:33</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0324</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Cultural activities</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Organizing Awareness Campaign/ Program including Nukkad Natak/Street Play on Maternal and Child health</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Matsaya Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:15:14</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0325</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp about child heath through campaign</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp about child heath through campaign</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp about child heath through campaign</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Janani Surakha Yojna - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:15:24</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0326</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp on institutional delivery and early registration to the hospitals for ante-natal chaeck up &amp; post natal check up of pregnanat mothers</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Ayushman Bharat - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:15:34</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0327</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Theme 2 - Healthy Village</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp on rountine immunization of children</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Family welfare</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp on rountine immunization of children</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Organizing awareness camp on rountine immunization of children</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>National Biogas and Manure Management Programme - Center Scheme</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>Training/Capacity Building</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:16:15</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0328</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Theme 5 - Clean and Green Village</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Creation, repair and maintenance of Drainage line for grey water</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sanitation</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Nali Nirman kary</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Creation, repair and maintenance of Drainage line for grey water</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:16:27</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0329</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Theme 5 - Clean and Green Village</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Construction of toilets in public institutions</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Sanitation</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Sochalay nirman</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Construction of toilets in public institutions</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:16:38</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0330</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Theme 5 - Clean and Green Village</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Construction of compost pits at community level</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sanitation</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>compost pit</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Construction of compost pits at community level</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:16:50</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0331</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Theme 4 - Water Sufficient Village</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Providing taps for drinking, handwashing and use in toilets in public institutions like schools, anganwadi centres, ashramshalas (tribal residential schools), health centres, GP buildings, public places like weekly haat/ bazar, mela ground, bus stand, playground/ sports complex, etc.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Drinking water</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>tanki nirman</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Providing taps for drinking, handwashing and use in toilets in public institutions like schools, anganwadi centres, ashramshalas (tribal residential schools), health centres, GP buildings, public places like weekly haat/ bazar, mela ground, bus stand, playground/ sports complex, etc.</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:17:02</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0332</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Theme 4 - Water Sufficient Village</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Providing taps for drinking, handwashing and use in toilets in public institutions like schools, anganwadi centres, ashramshalas (tribal residential schools), health centres, GP buildings, public places like weekly haat/ bazar, mela ground, bus stand, playground/ sports complex, etc.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Drinking water</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>motor pump</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Providing taps for drinking, handwashing and use in toilets in public institutions like schools, anganwadi centres, ashramshalas (tribal residential schools), health centres, GP buildings, public places like weekly haat/ bazar, mela ground, bus stand, playground/ sports complex, etc.</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:17:13</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0333</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boundry wall nirman </t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr"/>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:17:25</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0334</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boundry wall nirman </t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:17:36</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0335</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Roads, culverts, bridges, ferries, waterways, and other means of communication</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Roads</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Road nirman kary</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Roads, culverts, bridges, ferries, waterways, and other means of communication</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr"/>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:17:47</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0336</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Roads, culverts, bridges, ferries, waterways, and other means of communication</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Roads</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Road nirman kary</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Roads, culverts, bridges, ferries, waterways, and other means of communication</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:18:00</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0337</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>chabutara nirman kary</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:18:11</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0338</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Kitchen Shed Building</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>shed nirman kary</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Kitchen Shed Building</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:18:24</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0339</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Paver Blocks for Better Roads, culverts, bridges, ferries, waterways, and other means of communication and Public Spaces.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Roads</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pavar block </t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Construction of Paver Blocks for Better Roads, culverts, bridges, ferries, waterways, and other means of communication and Public Spaces.</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:19:06</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0340</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>strit light</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:19:18</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0341</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>bhawan marammat kary</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Construction of GP Building, Public Building/ community kitchen, Hall, Community Centre, Boundary wall, Flooring, doors, window, fixtures etc of Community Assets/public buildings/offices.</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:19:30</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0342</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Procurement of Furniture</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Furniture </t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Procurement of Furniture</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:20:12</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0343</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Construction/Establishment of Retaining Walls/ Fences</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Retaining wall</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Construction/Establishment of Retaining Walls/ Fences</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:20:24</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0344</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Fair Price Shops (PDS Shop) in villages</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Public distribution system</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>uchit muly dukan</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Fair Price Shops (PDS Shop) in villages</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:20:36</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0345</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Green Fencing and Plantation</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Social forestry and farm forestry</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>vrakshropan kary</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Green Fencing and Plantation</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>110000</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:21:17</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ACT-0346</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Theme 6 - Self-sufficient Infrastructure in Village</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Construction/Establishment of Retaining Walls/ Fences</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance of community system</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Community Works</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Fencing kary</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>New/Fresh</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Construction/Establishment of Retaining Walls/ Fences</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>Save and Forward</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01 01:21:29</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -894,7 +6642,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -906,7 +6654,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -942,7 +6690,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>855.3</t>
         </is>
       </c>
     </row>
@@ -954,7 +6702,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31 12:23:00</t>
+          <t>2026-09-01 01:21:29</t>
         </is>
       </c>
     </row>
